--- a/output_excel/16704681.xlsx
+++ b/output_excel/16704681.xlsx
@@ -470,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -479,14 +479,13 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="55" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -522,40 +521,35 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Lado Forte</t>
+          <t>Metragem</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Metragem</t>
+          <t>Material</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Altura Poste</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Altura Poste</t>
+          <t>Informações</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Informações</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Corrigido IA</t>
         </is>
@@ -589,21 +583,20 @@
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>7 0 4 6 112,5KVA 3 | P1-11 PROJETO 1x4ANA | 39 2 V1-3 B1F | TX10 | (DCIM) MENDES | ETAPA 3 | V1-2</t>
         </is>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="K2" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -631,31 +624,30 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>CONCRETO</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
           <t>NF | CONEX. | P2 | V1-2 | CORDOALHA BT0 | C12X600112,5KVAU4112,5KVAET1A112,5KVAIP | BF-A 552810 | S44(2)112,5KVASMPI (DCIM)</t>
         </is>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="K3" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -686,28 +678,27 @@
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>55.89m</t>
         </is>
       </c>
+      <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>BT 1X4ANA(4AN) 3X1/0AN 47.51M 47.51M | (DCIM) | 55.89M | V1-2 | (DCIM) MENDES | (DCIM) BT 1 CONEX. 4 112,5KVA 1x4ANA 112,5KVA 2x1/0AN(4AN) 112,5KVA 2x1/0AN(4AN) | CORDOALHA BT0</t>
         </is>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="K4" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -734,28 +725,27 @@
       </c>
       <c r="E5" s="2" t="inlineStr"/>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>50.10m</t>
         </is>
       </c>
+      <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>BT MT 3X1/0AN 1x4ANA 50.10M 50.10M | M12X230112,5KVAB1M112,5KVAS43(3)112,5KVAIP | xP8 CONEX. xBM | M12X600112,5KVA2X[U3]112,5KVABF-T112,5KVAS44(3)112,5KVAIP 1 TX10 2 V1-3 16M | (DCIM) | DIMENSIONAR ELO 6K | S44(2)112,5KVASMPI (DCIM) | P31 S44(3)112,5KVASMTR</t>
         </is>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="K5" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="L5" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -791,31 +781,30 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>CONCRETO</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
           <t>C12X600112,5KVAU4112,5KVAET1A112,5KVAIP | P31 S44(3)112,5KVASMTR | (DCIM) 2 CS´S | PODA 175ET005296879 509331 | PODA REAPLICAR OUTRO LADO POSTE | xP8 CONEX. xBM | (DCIM)</t>
         </is>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="K6" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="M6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -843,31 +832,30 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>CONCRETO</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
           <t>(DCIM) C12X600112,5KVAU4112,5KVABF-A112,5KVAIP | CORDOALHA BT0 | V8-4 | C12X600112,5KVAU4112,5KVAET1A112,5KVAIP | S44(2)112,5KVASMPI (DCIM) | V2-8 | (DCIM) | P31 S44(3)112,5KVASMTR</t>
         </is>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="K7" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="M7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -894,28 +882,27 @@
       </c>
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>41.06m</t>
         </is>
       </c>
+      <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>MT BT 3X1/0AN 1x4ANA 41.06M 41.06M | (DCIM) | xP8 CONEX. xBM | S44(2)112,5KVASMTR (DCIM) | P31 S44(3)112,5KVASMTR | M12X230112,5KVAB1M112,5KVAS43(3)112,5KVAIP | (DCIM) APARECIDINHA CARGA 1x4ANA | M12X150112,5KVAB4M112,5KVAET1A112,5KVAS44(3)112,5KVAL1(2)112,5KVAIP</t>
         </is>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="K8" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="M8" s="3" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -942,7 +929,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>AVENIDA 2 CS</t>
+          <t>RUA AV. W</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -951,31 +938,30 @@
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>CONCRETO</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
           <t>C12X300112,5KVAU4112,5KVAIP M12X600112,5KVAU4112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | CONEX. | (DCIM) APARECIDINHA CARGA 1x4ANA | C12X600112,5KVAU4112,5KVAET1A112,5KVAIP</t>
         </is>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="K9" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="M9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1002,28 +988,27 @@
       </c>
       <c r="E10" s="2" t="inlineStr"/>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>59.40m</t>
         </is>
       </c>
+      <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>BT 3X1/0AN 59.40M 59.40M | 2 V1-3 27M | (DCIM) APARECIDINHA CARGA 1x4ANA | 17048849 17049010 2 V1-3 2 V1-3 (DCIM) NOTAS | CABOS CLANDESTINOS: LOCAL COMPARTILHANTES | V4-5 | M12X300112,5KVAU2112,5KVAS43(3)112,5KVAL1(2)112,5KVAIP | (DCIM) 2 CS´S</t>
         </is>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="K10" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="M10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1059,31 +1044,30 @@
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>CONCRETO</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
           <t>C12X300112,5KVAU4112,5KVAIP M12X600112,5KVAU4112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | (DCIM) 112,5KVA FONTE | (DCIM) APARECIDINHA CARGA 1x4ANA | 1x4ANA 2 CS's AVENIDA | 2 V1-3 7275</t>
         </is>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="K11" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="M11" s="4" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1110,28 +1094,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>38.93m</t>
         </is>
       </c>
+      <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>BT 1x4ANA 3X1/0AN 38.93M 38.93M | BT 1x4ANA 3X1/0AN 40.95M 40.95M | M12X300112,5KVAU2112,5KVAS43(3)112,5KVAL1(2)112,5KVAIP | 2 V1-3 27M | V5-6 | (DCIM) APARECIDINHA CARGA 1x4ANA | BT 3X1/0AN 59.40M 59.40M | 5 TX10 2 V1-3 75M</t>
         </is>
       </c>
-      <c r="L12" s="3" t="n">
+      <c r="K12" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="M12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1159,31 +1142,30 @@
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>CONCRETO</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
           <t>CONEX. 3 RAMAIS LC P5 | C12X300112,5KVAU4112,5KVAIP | M12X300112,5KVAU2112,5KVAS43(3)112,5KVAL1(2)112,5KVAIP | C12X300112,5KVAU4112,5KVAIP M12X600112,5KVAU4112,5KVAS43(3)112,5KVAL1(1)112,5KVAIP | TRAFO LADO | C12X600112,5KVACEAFC4112,5KVAIP | FAZER CACHIMBO | P6</t>
         </is>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="K13" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="M13" s="4" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1214,28 +1196,27 @@
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>40.95m</t>
         </is>
       </c>
+      <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>BT 1x4ANA 3X1/0AN 40.95M 40.95M | BT 1x4ANA 3X1/0AN 38.93M 38.93M | CONEX. M12X600112,5KVAU4112,5KVAS44(1)112,5KVAS44(2)112,5KVAL1(2)112,5KVAIP | M12X300112,5KVAU2112,5KVAS43(3)112,5KVAL1(2)112,5KVAIP | V6-7 | 3 TX10 2 V1-3 37.90M | FAZER CACHIMBO</t>
         </is>
       </c>
-      <c r="L14" s="3" t="n">
+      <c r="K14" s="3" t="n">
         <v>55</v>
       </c>
-      <c r="M14" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>CRITICO</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1262,7 +1243,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>AVENIDA 2 CS</t>
+          <t>RUA 112,5KVA P7X</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1271,31 +1252,30 @@
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>CONCRETO</t>
+        </is>
+      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>CONCRETO</t>
+          <t>12m</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>C12X600112,5KVACEAFC4112,5KVAIP | CONEX. M12X600112,5KVAU4112,5KVAS44(1)112,5KVAS44(2)112,5KVAL1(2)112,5KVAIP | CONEX. 3 RAMAIS LC P5 | C12X300112,5KVAU4112,5KVAIP | M12X300112,5KVAU2112,5KVAS43(3)112,5KVAL1(2)112,5KVAIP | BT 1RU6A 112,5KVA P7x | FAZER CACHIMBO</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="n">
+          <t>C12X600112,5KVACEAFC4112,5KVAIP | CONEX. M12X600112,5KVAU4112,5KVAS44(1)112,5KVAS44(2)112,5KVAL1(2)112,5KVAIP | CONEX. 3 RAMAIS LC P5 | C12X300112,5KVAU4112,5KVAIP | M12X300112,5KVAU2112,5KVAS43(3)112,5KVAL1(2)112,5KVAIP | FAZER CACHIMBO</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="M15" s="4" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>REVISAR</t>
         </is>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
